--- a/TASTI_SYNTHETIC/PnoDProg.xlsx
+++ b/TASTI_SYNTHETIC/PnoDProg.xlsx
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>85D239D610</t>
+          <t>22W503J950</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10P253K523</t>
+          <t>87V978M659</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -470,7 +470,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>22N228N409</t>
+          <t>72Q802Q143</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -487,7 +487,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>50E261S769</t>
+          <t>81S911U956</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -504,7 +504,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>84D111R914</t>
+          <t>88L503E484</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -521,7 +521,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>86C960F861</t>
+          <t>33X120P251</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -538,7 +538,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>43X581D604</t>
+          <t>76Z348F714</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>74W763Q166</t>
+          <t>60F381Q350</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>31F418Q328</t>
+          <t>83T570D824</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -589,7 +589,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>93Z199U502</t>
+          <t>71G357S277</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -606,7 +606,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>82A162A454</t>
+          <t>23H304L521</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -623,7 +623,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>54K361S958</t>
+          <t>91S151D928</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -640,7 +640,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>52T792T906</t>
+          <t>34B228M483</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -657,7 +657,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>58R592T780</t>
+          <t>85X133F710</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -674,7 +674,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>83L567E990</t>
+          <t>37C398L473</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>41J314X437</t>
+          <t>44U263F997</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -708,7 +708,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>84E876F942</t>
+          <t>34D974H198</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -725,7 +725,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>77H197G594</t>
+          <t>42B600M954</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -742,7 +742,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>74M828H595</t>
+          <t>33S799G332</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -759,7 +759,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>57J247A423</t>
+          <t>55N100C809</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -776,7 +776,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>26T952W592</t>
+          <t>42X959K518</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>53U173S159</t>
+          <t>60F560L622</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -810,7 +810,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>93V398B625</t>
+          <t>59K513J705</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -827,7 +827,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>53Q962L635</t>
+          <t>84B782D922</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -844,7 +844,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>17S621Z413</t>
+          <t>62X615Y416</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -861,7 +861,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>47Q811G625</t>
+          <t>22G670L626</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -878,7 +878,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>81B347Y897</t>
+          <t>38K178V637</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>57Y952L149</t>
+          <t>40T511X556</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>91G675F924</t>
+          <t>92L250J400</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -929,7 +929,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>98L783J442</t>
+          <t>45B703K429</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>47Y452P901</t>
+          <t>95T916C576</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -963,7 +963,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>37V910V847</t>
+          <t>81N249E867</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -980,7 +980,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>68R278X348</t>
+          <t>62R227X543</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -997,7 +997,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>35F678D199</t>
+          <t>52G778N780</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>83N504R821</t>
+          <t>74Z908R199</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1031,7 +1031,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>42X596Q778</t>
+          <t>92L140U513</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>83Z803N519</t>
+          <t>65N111D228</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1065,7 +1065,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>21N406C312</t>
+          <t>50M338L643</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1082,7 +1082,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>49X916Y546</t>
+          <t>21G860N603</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1099,7 +1099,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>68J908Y990</t>
+          <t>77M130P802</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1116,7 +1116,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>72G929R540</t>
+          <t>23Q122J110</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1133,7 +1133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>89M113W689</t>
+          <t>64S206J658</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1150,7 +1150,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20V781D968</t>
+          <t>57Z324T171</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1167,7 +1167,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>75K172D318</t>
+          <t>45G743B510</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1184,7 +1184,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>36B855W582</t>
+          <t>29B475X788</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1201,7 +1201,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>75M377X393</t>
+          <t>28V393D889</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1218,7 +1218,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>13G631Q917</t>
+          <t>38G880Q418</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1235,7 +1235,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>94T122W472</t>
+          <t>39U325W423</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1252,7 +1252,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>96F454U281</t>
+          <t>69J573F186</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1269,7 +1269,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>24T620Z903</t>
+          <t>66A191X255</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1286,7 +1286,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>48Z180M421</t>
+          <t>62E642X436</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>71K687F611</t>
+          <t>80A147K559</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1320,7 +1320,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>72Y641E397</t>
+          <t>67D408D408</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1337,7 +1337,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>19M522A643</t>
+          <t>25C689M338</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1354,7 +1354,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>72N384N965</t>
+          <t>16Q432Z475</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1371,7 +1371,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>64T912F528</t>
+          <t>97Z114W907</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1388,7 +1388,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>91S330N870</t>
+          <t>72P377B703</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1405,7 +1405,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>33L408G683</t>
+          <t>42M191J314</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1422,7 +1422,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>81K873R241</t>
+          <t>31K543T565</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1439,7 +1439,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>23B741L110</t>
+          <t>33G971P226</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1456,7 +1456,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>60Q934F246</t>
+          <t>96T917A787</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>24Y554L387</t>
+          <t>81J932M634</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1490,7 +1490,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>68P912E756</t>
+          <t>69U108P553</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1507,7 +1507,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>69A655F760</t>
+          <t>41E182F976</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1524,7 +1524,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>63J963M780</t>
+          <t>57U201Y336</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1541,7 +1541,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>36R950M288</t>
+          <t>47L157X523</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1558,7 +1558,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>13F639Q182</t>
+          <t>84Y523A493</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1575,7 +1575,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>75N429H770</t>
+          <t>91X106C986</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1592,7 +1592,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>58R504U661</t>
+          <t>18T780L751</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1609,7 +1609,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>65L940V808</t>
+          <t>95L119H755</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1626,7 +1626,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>95H905L765</t>
+          <t>74S621W887</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1643,7 +1643,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>78A475B370</t>
+          <t>96T171K756</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1660,7 +1660,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>97L201T734</t>
+          <t>58V635X463</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1677,7 +1677,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>56W686D744</t>
+          <t>42R331F742</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1694,7 +1694,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>37F338Z712</t>
+          <t>81D437V902</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>44Z987M139</t>
+          <t>44J638H988</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1728,7 +1728,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>87S576U315</t>
+          <t>77T525Z815</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1745,7 +1745,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>16W127P518</t>
+          <t>30K485G670</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1762,7 +1762,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>66C382H260</t>
+          <t>51R338Q719</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1779,7 +1779,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>21S905T489</t>
+          <t>93Y468Z144</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1796,7 +1796,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>29P452J507</t>
+          <t>83N295P947</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1813,7 +1813,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>90Q787J936</t>
+          <t>62J701X643</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1830,7 +1830,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>94U728B872</t>
+          <t>43M508D270</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -1847,7 +1847,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>18L926D746</t>
+          <t>21G217G570</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -1864,7 +1864,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>48R922Z273</t>
+          <t>61Q769H106</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -1881,7 +1881,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>27Z389H980</t>
+          <t>42H991S513</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -1898,7 +1898,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>27P968J124</t>
+          <t>60W536V215</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>76S244D539</t>
+          <t>80R551T967</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -1932,7 +1932,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>63R361A274</t>
+          <t>94S981K959</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -1949,7 +1949,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>50N806T734</t>
+          <t>11Y634W798</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -1966,7 +1966,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>81V627K953</t>
+          <t>61A917T660</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -1983,7 +1983,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>14J714Z690</t>
+          <t>39M804H255</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2000,7 +2000,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>71B409R713</t>
+          <t>36N830Y955</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2017,7 +2017,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>82S153M179</t>
+          <t>55J670U553</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2034,7 +2034,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>69G301K967</t>
+          <t>24D284G470</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2051,7 +2051,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>42Z326K706</t>
+          <t>26N300T834</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2068,7 +2068,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>92P620Q298</t>
+          <t>13G693E170</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2085,7 +2085,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>43V820R208</t>
+          <t>89C231S539</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2102,7 +2102,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>42W684N943</t>
+          <t>56F880D533</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2119,7 +2119,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>64R336U638</t>
+          <t>88N769P956</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2136,7 +2136,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>67A576C126</t>
+          <t>87Y590Y735</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2153,7 +2153,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>15C527U481</t>
+          <t>11Q824D897</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2170,7 +2170,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>21V393J212</t>
+          <t>51U390K672</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2187,7 +2187,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>32X899R844</t>
+          <t>75G690Z437</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2204,7 +2204,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>23W576Y347</t>
+          <t>76W762R342</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2221,7 +2221,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>80M878L851</t>
+          <t>15T281N954</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2238,7 +2238,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>23H292K832</t>
+          <t>13U751T255</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2255,7 +2255,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>77H566Z746</t>
+          <t>34T221X485</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2272,7 +2272,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>67G568F455</t>
+          <t>82G882W445</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2289,7 +2289,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>40A338W785</t>
+          <t>68X633Z597</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2306,7 +2306,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>97F245Y918</t>
+          <t>95S139K128</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2323,7 +2323,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>77N919F481</t>
+          <t>24Z394E314</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2340,7 +2340,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>47M620L120</t>
+          <t>40A385N903</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>70Z915D258</t>
+          <t>47W925W104</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2374,7 +2374,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>72X586B720</t>
+          <t>36R551K505</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2391,7 +2391,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>59P740N112</t>
+          <t>38E374N571</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2408,7 +2408,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>64N786A423</t>
+          <t>38S553N137</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>32Z493G670</t>
+          <t>74D948R273</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2442,7 +2442,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>89E455J931</t>
+          <t>48R736F627</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>14Q159V555</t>
+          <t>89L807Q959</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>33Y872L498</t>
+          <t>59B598A240</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2493,7 +2493,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>50W682Y109</t>
+          <t>31F231B437</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2510,7 +2510,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>27P844K931</t>
+          <t>47R254C942</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -2527,7 +2527,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>28Q237G544</t>
+          <t>69V958F630</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -2544,7 +2544,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>82F575V341</t>
+          <t>62V738Y137</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2561,7 +2561,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>67Q602A487</t>
+          <t>60C775S877</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2578,7 +2578,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>74N301A103</t>
+          <t>39K886J969</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2595,7 +2595,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>45C102Z677</t>
+          <t>11W939A452</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2612,7 +2612,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>53Y548K970</t>
+          <t>17V954X474</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -2629,7 +2629,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>61V451V910</t>
+          <t>50Q876L468</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -2646,7 +2646,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>91G126H718</t>
+          <t>56P582W319</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -2663,7 +2663,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>61E258E498</t>
+          <t>87S803B764</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -2680,7 +2680,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>33V692Y641</t>
+          <t>82W921M339</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -2697,7 +2697,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>57U894G569</t>
+          <t>54E131L735</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -2714,7 +2714,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>13J611X980</t>
+          <t>44B132J361</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -2731,7 +2731,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>33L501B318</t>
+          <t>78N508Z545</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -2748,7 +2748,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>19F796E546</t>
+          <t>46V480X468</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -2765,7 +2765,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>71A182Q676</t>
+          <t>13A666N139</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -2782,7 +2782,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>26E730D265</t>
+          <t>19M722F203</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -2799,7 +2799,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>22N425C599</t>
+          <t>86A306Z592</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -2816,7 +2816,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>78M642B615</t>
+          <t>90A798H601</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -2833,7 +2833,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>69Q475T711</t>
+          <t>97T119F252</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -2850,7 +2850,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>14P431Y766</t>
+          <t>61U608T716</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -2867,7 +2867,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>48R691E783</t>
+          <t>59A848P258</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -2884,7 +2884,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>92A956W493</t>
+          <t>70J440D187</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -2901,7 +2901,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>40W806F802</t>
+          <t>70Q803F819</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -2918,7 +2918,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>59C166N634</t>
+          <t>43Z897K778</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -2935,7 +2935,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>48A330D609</t>
+          <t>61D563S544</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -2952,7 +2952,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>29C287Q104</t>
+          <t>88B352V994</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -2969,7 +2969,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>19K397J946</t>
+          <t>37G152U985</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -2986,7 +2986,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>44V118B988</t>
+          <t>57V799D951</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3003,7 +3003,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>14T315R658</t>
+          <t>44C653U519</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3020,7 +3020,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>96V437M154</t>
+          <t>38B195C953</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3037,7 +3037,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>40A385N903</t>
+          <t>20R408A929</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -3054,7 +3054,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>49M335P320</t>
+          <t>90U513U341</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -3071,7 +3071,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>56P115M764</t>
+          <t>36M388L108</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -3088,7 +3088,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>89K157B866</t>
+          <t>88P848X966</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -3105,7 +3105,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>80U145Y815</t>
+          <t>75T592U219</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -3122,7 +3122,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>23C783Y696</t>
+          <t>79W428H384</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -3139,7 +3139,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>88S840V682</t>
+          <t>15M456C885</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -3156,7 +3156,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>89L218K963</t>
+          <t>70Z186V901</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -3173,7 +3173,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>71J223B266</t>
+          <t>37N358Y580</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -3190,7 +3190,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>38B790F133</t>
+          <t>85P440L610</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -3207,7 +3207,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>52N105K497</t>
+          <t>43K359P654</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -3224,7 +3224,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>13X668Z623</t>
+          <t>44T632M601</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -3241,7 +3241,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>23A433V455</t>
+          <t>84N838B423</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
